--- a/module4/miniproj1/planning.xlsx
+++ b/module4/miniproj1/planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/408a8262ffb9e406/organisedshare.ai/Institute of Data/2026-02-02-SE-FT-AP-A-B/institute-of-data-labs/module4/miniproj1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="211" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44E47CAE-F160-4616-B97D-8F72E87A2B38}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFA27789-27AC-44B9-A591-C535CC7955D8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Landing Page" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
   <si>
     <t>Share price</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>EV</t>
-  </si>
-  <si>
-    <t>Login</t>
   </si>
   <si>
     <t>Trailing PE</t>
@@ -145,13 +142,37 @@
   <si>
     <t xml:space="preserve">Mary Momentus
 </t>
+  </si>
+  <si>
+    <t>Deep value</t>
+  </si>
+  <si>
+    <t>AQZ-AU</t>
+  </si>
+  <si>
+    <t>GTLB-US</t>
+  </si>
+  <si>
+    <t>Profitable Growth</t>
+  </si>
+  <si>
+    <t>mobile gossip monitor</t>
+  </si>
+  <si>
+    <t>SAFE-US</t>
+  </si>
+  <si>
+    <t>RBRK-US</t>
+  </si>
+  <si>
+    <t>Unprofitable Growth</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,13 +201,46 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color rgb="FF7030A0"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FF067CE8"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -201,12 +255,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -221,12 +272,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF067CE8"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -236,6 +304,211 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>44823</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>166321</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>422136</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>60510</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90EC6068-4CFC-A7A3-FBAA-228F3168E913}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="649941" y="547321"/>
+          <a:ext cx="2853813" cy="2874953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>82766</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>36175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>460079</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>143275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F26964F-9A68-1926-61AD-0EC6788E2926}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="687884" y="4271999"/>
+          <a:ext cx="2853813" cy="2874953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>64677</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>40498</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>441990</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>147598</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{993681BC-7837-B8D7-DF11-B57D5DD6ED45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="669795" y="8321645"/>
+          <a:ext cx="2853813" cy="2874953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>46589</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>78439</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>423902</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>185539</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2206F4D1-5C5C-FA55-BF37-FE2D05DF1D1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="651707" y="12360086"/>
+          <a:ext cx="2853813" cy="2874953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -505,16 +778,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3553A85-7BAF-48B3-BDA8-F22B13EECACD}">
-  <dimension ref="B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:C80"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="7"/>
+    <col min="3" max="3" width="28" style="7" customWidth="1"/>
+    <col min="4" max="7" width="9.140625" style="7"/>
+    <col min="8" max="8" width="22.5703125" style="7" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="7"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>6</v>
+    <row r="2" spans="2:2" s="7" customFormat="1" ht="45.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" s="7" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="C19" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="C20" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" s="7" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="C37" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="C38" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3" s="7" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="C58" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="C59" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" spans="3:3" s="7" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="C79" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="C80" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -523,67 +844,67 @@
   <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="29.85546875" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>35</v>
+      <c r="A3" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="3"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -658,145 +979,147 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+      <c r="A17" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D22" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="C25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C28" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E33" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="E32" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="E33" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="B38" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/module4/miniproj1/planning.xlsx
+++ b/module4/miniproj1/planning.xlsx
@@ -8,26 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/408a8262ffb9e406/organisedshare.ai/Institute of Data/2026-02-02-SE-FT-AP-A-B/institute-of-data-labs/module4/miniproj1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="306" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFA27789-27AC-44B9-A591-C535CC7955D8}"/>
+  <xr:revisionPtr revIDLastSave="491" documentId="11_F25DC773A252ABDACC104861915A7E145BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{328ADCC9-6D76-457B-8018-D42F96D8B3F4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Landing Page" sheetId="2" r:id="rId1"/>
-    <sheet name="Share Price Chart" sheetId="1" r:id="rId2"/>
-    <sheet name="Hardcode Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Share Price Chart - array" sheetId="1" r:id="rId2"/>
+    <sheet name="Share Price Chart - actual" sheetId="4" r:id="rId3"/>
+    <sheet name="Requirements" sheetId="5" r:id="rId4"/>
+    <sheet name="Add stock" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="62">
   <si>
     <t>Share price</t>
   </si>
@@ -87,9 +100,6 @@
   </si>
   <si>
     <t>"Stock code" = "RBRK-US"</t>
-  </si>
-  <si>
-    <t>"Stock code" = "GTLB-US"</t>
   </si>
   <si>
     <t>Dividend yield</t>
@@ -150,29 +160,80 @@
     <t>AQZ-AU</t>
   </si>
   <si>
-    <t>GTLB-US</t>
-  </si>
-  <si>
     <t>Profitable Growth</t>
   </si>
   <si>
     <t>mobile gossip monitor</t>
   </si>
   <si>
+    <t>Unprofitable Growth</t>
+  </si>
+  <si>
+    <t>Landing page containing 4 lense categories</t>
+  </si>
+  <si>
+    <t>https://echarts.apache.org/examples/en/editor.html?c=line-sections</t>
+  </si>
+  <si>
+    <t>"Stock code" = "360-AU"</t>
+  </si>
+  <si>
+    <t>360-AU</t>
+  </si>
+  <si>
+    <t>Defensive Yield</t>
+  </si>
+  <si>
+    <t>RBRK-US</t>
+  </si>
+  <si>
     <t>SAFE-US</t>
   </si>
   <si>
-    <t>RBRK-US</t>
-  </si>
-  <si>
-    <t>Unprofitable Growth</t>
+    <t>Share price chart cards page, divisible by category</t>
+  </si>
+  <si>
+    <t>Different data shown for each share price</t>
+  </si>
+  <si>
+    <t>navbar</t>
+  </si>
+  <si>
+    <t>ALL STOCKS</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>stock cards</t>
+  </si>
+  <si>
+    <t>add stock</t>
+  </si>
+  <si>
+    <t>Aim:</t>
+  </si>
+  <si>
+    <t>I want to monitor watchlist of stocks on a small mobile screen divided by lenses.</t>
+  </si>
+  <si>
+    <t>I want to see each stock's key metrics according to their lense category.</t>
+  </si>
+  <si>
+    <t>Long term the aim is to monitor stocks on a virtual holographic or VR screen so I can work on stocks anywhere, even during a meeting.</t>
+  </si>
+  <si>
+    <t>Long term I should be able to start working on a stock when friends tell me about their stock. That way I can sell my product while also save time researching things.</t>
+  </si>
+  <si>
+    <t>I want ability to add stocks quickly to watchlist and start researching it when gossiping with peers.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,8 +289,22 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -239,6 +314,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -255,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -284,6 +365,18 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -310,23 +403,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>44823</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>166321</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>422136</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>60510</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1115220</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>169853</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90EC6068-4CFC-A7A3-FBAA-228F3168E913}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF850318-FBED-4AF7-BDD5-E55B01FED580}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -348,7 +441,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="649941" y="547321"/>
+          <a:off x="400050" y="771525"/>
           <a:ext cx="2853813" cy="2874953"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -360,23 +453,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>82766</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>36175</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>460079</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>143275</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>1431227</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>141278</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F26964F-9A68-1926-61AD-0EC6788E2926}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29500D8E-6CE1-45FA-8536-6AD1AA03E3A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -398,7 +491,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="687884" y="4271999"/>
+          <a:off x="13563600" y="742950"/>
           <a:ext cx="2853813" cy="2874953"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -410,23 +503,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>64677</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>40498</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>441990</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>147598</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>775122</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>26978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{993681BC-7837-B8D7-DF11-B57D5DD6ED45}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FE76859-292A-46C2-AB21-AFA4ABE69AD9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -448,7 +541,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="669795" y="8321645"/>
+          <a:off x="20288250" y="819150"/>
           <a:ext cx="2853813" cy="2874953"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -460,23 +553,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>46589</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>78439</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>423902</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>185539</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1392331</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
+        <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2206F4D1-5C5C-FA55-BF37-FE2D05DF1D1E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAF9859E-C867-7769-0661-F948EF6FD7CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -498,8 +591,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="651707" y="12360086"/>
-          <a:ext cx="2853813" cy="2874953"/>
+          <a:off x="7096124" y="666749"/>
+          <a:ext cx="2952751" cy="2952751"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -509,10 +602,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -778,64 +867,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3553A85-7BAF-48B3-BDA8-F22B13EECACD}">
-  <dimension ref="B2:C80"/>
+  <dimension ref="B2:F77"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="7"/>
     <col min="3" max="3" width="28" style="7" customWidth="1"/>
-    <col min="4" max="7" width="9.140625" style="7"/>
+    <col min="4" max="4" width="12.140625" style="7" customWidth="1"/>
+    <col min="5" max="7" width="9.140625" style="7"/>
     <col min="8" max="8" width="22.5703125" style="7" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" s="7" customFormat="1" ht="45.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" ht="45.75" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" s="7" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="C19" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="C20" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="C37" s="9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="3:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="C20" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="3:3" s="7" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="C37" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="3:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="C38" s="9" t="s">
+    <row r="57" spans="3:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="C57" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="3:3" s="7" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="C58" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="3:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="C59" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="79" spans="3:3" s="7" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="C79" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="80" spans="3:3" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="C80" s="9" t="s">
-        <v>41</v>
+    <row r="77" spans="3:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="C77" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -856,7 +944,7 @@
     </row>
     <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
@@ -867,7 +955,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>19</v>
@@ -878,21 +966,21 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>13</v>
@@ -993,7 +1081,7 @@
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1016,10 +1104,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1035,21 +1123,21 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1070,56 +1158,56 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E32" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E33" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1128,10 +1216,416 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDECC567-1197-4F91-930D-983B0E643FC2}">
+  <dimension ref="A2:AE47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+    <col min="12" max="12" width="24.7109375" customWidth="1"/>
+    <col min="20" max="20" width="19.85546875" customWidth="1"/>
+    <col min="21" max="21" width="24.7109375" customWidth="1"/>
+    <col min="29" max="29" width="9.140625" customWidth="1"/>
+    <col min="30" max="30" width="23.5703125" customWidth="1"/>
+    <col min="31" max="31" width="24.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:31" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="3:31" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE3" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" ht="18" x14ac:dyDescent="0.25">
+      <c r="C20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="U20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE20" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="AD27" s="1"/>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD28" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="K29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="AD29" s="1"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="AD30" s="1"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="AD31" s="1"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="AD32" s="1"/>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="AD33" s="1"/>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="T34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD34" s="1"/>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD35" s="1"/>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T36" s="1"/>
+      <c r="AD36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T37" s="1"/>
+      <c r="AD37" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="K38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T38" s="1"/>
+      <c r="AD38" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="AD39" s="1"/>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="K40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD40" s="1"/>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="K41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD41" s="1"/>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="AD42" s="1"/>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="T43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD43" s="1"/>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="AD44" s="1"/>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="AD45" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="AD46" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDF7C372-B9F5-4F99-9640-73AC8C3D0BD2}">
+  <dimension ref="B2:L17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBEDB303-8C6A-478D-BB39-4AA40CF6AEA0}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="4" max="4" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>